--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2F7678-A711-4802-B155-F73F379662E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91640AC9-1789-4FD7-83DD-F6C5E3673A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3015" yWindow="2460" windowWidth="25455" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>Category</t>
   </si>
@@ -349,6 +349,18 @@
   </si>
   <si>
     <t>email agent</t>
+  </si>
+  <si>
+    <t>Agentic RAG</t>
+  </si>
+  <si>
+    <t>Definition and difference fro traditional RAG</t>
+  </si>
+  <si>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -1002,26 +1014,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="4"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="3">
-        <v>30</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>75</v>
-      </c>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -1031,13 +1026,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1045,13 +1040,16 @@
         <v>91</v>
       </c>
       <c r="B27" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>77</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1062,10 +1060,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,73 +1071,60 @@
         <v>91</v>
       </c>
       <c r="B29" s="3">
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="3">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="3">
-        <v>35</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="3">
-        <v>40</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="3">
-        <v>35</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" t="s">
-        <v>49</v>
-      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -1149,191 +1134,250 @@
         <v>30</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="B36" s="3">
+        <v>35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="B37" s="3">
+        <v>40</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
+      </c>
+      <c r="D37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="3"/>
+      <c r="A38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="3">
+        <v>35</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="3">
+        <v>30</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="3">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>103</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="3">
-        <v>25</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" s="3">
-        <v>30</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="3">
-        <v>25</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" t="s">
-        <v>59</v>
+      <c r="B44" s="3">
+        <v>30</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B45" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B46" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B47" s="3">
         <v>25</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B49" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B50" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B51" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="3">
+        <v>60</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="3">
+        <v>30</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="3">
+        <v>20</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D57" t="s">
         <v>100</v>
       </c>
     </row>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\AgenticAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91640AC9-1789-4FD7-83DD-F6C5E3673A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BDE113-D570-4C59-A710-EAC0ADF5F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="2460" windowWidth="25455" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="2850" windowWidth="25830" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
   <si>
     <t>Category</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Agent with Memory</t>
   </si>
   <si>
-    <t>Add memory using vector DB (FAISS)</t>
-  </si>
-  <si>
     <t>RAG + Agent</t>
   </si>
   <si>
@@ -361,6 +358,12 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>Add memory using vector DB (Using FAISS)</t>
+  </si>
+  <si>
+    <t>pdf + code done for ST/LT Memory</t>
   </si>
 </sst>
 </file>
@@ -726,12 +729,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -743,12 +746,12 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3">
         <v>25</v>
@@ -760,12 +763,12 @@
         <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -777,12 +780,12 @@
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="3">
         <v>30</v>
@@ -794,12 +797,12 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="3">
         <v>25</v>
@@ -811,29 +814,29 @@
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3">
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B9" s="3">
         <v>25</v>
@@ -845,12 +848,12 @@
         <v>16</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3">
         <v>30</v>
@@ -862,12 +865,12 @@
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3">
         <v>20</v>
@@ -881,7 +884,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" s="3">
         <v>25</v>
@@ -895,7 +898,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" s="3">
         <v>30</v>
@@ -909,7 +912,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3">
         <v>25</v>
@@ -923,7 +926,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3">
         <v>30</v>
@@ -932,15 +935,15 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3">
         <v>30</v>
@@ -952,12 +955,12 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="3">
         <v>25</v>
@@ -969,7 +972,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -977,15 +980,15 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="3">
         <v>20</v>
@@ -999,19 +1002,19 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1020,7 +1023,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="3">
         <v>30</v>
@@ -1032,12 +1035,12 @@
         <v>35</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="3">
         <v>30</v>
@@ -1046,15 +1049,15 @@
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="3">
         <v>25</v>
@@ -1068,7 +1071,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" s="3">
         <v>25</v>
@@ -1080,12 +1083,12 @@
         <v>40</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3">
         <v>20</v>
@@ -1099,27 +1102,27 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1128,7 +1131,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B35" s="3">
         <v>30</v>
@@ -1137,15 +1140,15 @@
         <v>43</v>
       </c>
       <c r="D35" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3">
         <v>35</v>
@@ -1154,77 +1157,77 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="3">
         <v>40</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" t="s">
         <v>46</v>
-      </c>
-      <c r="D37" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="3">
         <v>35</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
         <v>48</v>
-      </c>
-      <c r="D38" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="3">
         <v>30</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" t="s">
         <v>102</v>
       </c>
-      <c r="D40" t="s">
-        <v>103</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1232,153 +1235,153 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="3">
+        <v>30</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="3">
-        <v>30</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" t="s">
         <v>52</v>
-      </c>
-      <c r="D44" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="3">
         <v>25</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
         <v>54</v>
-      </c>
-      <c r="D45" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="3">
         <v>30</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" t="s">
         <v>56</v>
-      </c>
-      <c r="D46" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="3">
         <v>25</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" t="s">
         <v>58</v>
-      </c>
-      <c r="D47" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="3">
+        <v>30</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="3">
-        <v>30</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" t="s">
         <v>61</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" s="3">
         <v>25</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
         <v>63</v>
-      </c>
-      <c r="D50" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" s="3">
         <v>25</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" t="s">
         <v>65</v>
-      </c>
-      <c r="D51" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B53" s="3">
         <v>60</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" t="s">
         <v>68</v>
-      </c>
-      <c r="D53" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" s="3">
         <v>30</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
         <v>70</v>
-      </c>
-      <c r="D54" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="3">
         <v>20</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" t="s">
         <v>72</v>
-      </c>
-      <c r="D55" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" t="s">
         <v>99</v>
-      </c>
-      <c r="D57" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BDE113-D570-4C59-A710-EAC0ADF5F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B301214C-6240-4222-BE52-14EB200BD93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="2850" windowWidth="25830" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25830" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
   <si>
     <t>Category</t>
   </si>
@@ -364,6 +364,12 @@
   </si>
   <si>
     <t>pdf + code done for ST/LT Memory</t>
+  </si>
+  <si>
+    <t>Agent types and evolution- optional</t>
+  </si>
+  <si>
+    <t>Simple reflex agent, Model agent, goal based, utility based agent, Learning agent, LLM agent</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -783,39 +789,25 @@
         <v>82</v>
       </c>
     </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="3">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="3">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="E6" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -825,10 +817,10 @@
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>74</v>
@@ -842,13 +834,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -859,13 +851,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,117 +865,106 @@
         <v>87</v>
       </c>
       <c r="B11" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="3">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="3">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B16" s="3">
         <v>25</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D16" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="3">
-        <v>30</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="3">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="3">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="3">
-        <v>30</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="3">
-        <v>25</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="3">
+        <v>30</v>
+      </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -991,99 +972,96 @@
         <v>89</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="3">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="3">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="4"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="3">
-        <v>30</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="3">
-        <v>30</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="3">
-        <v>25</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
-      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B29" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,101 +1069,107 @@
         <v>90</v>
       </c>
       <c r="B30" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>76</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="B31" s="3">
+        <v>25</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="3">
+        <v>25</v>
+      </c>
       <c r="C32" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>108</v>
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D33" s="4"/>
-      <c r="E33" s="3"/>
+      <c r="A33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="3">
+        <v>20</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="3">
-        <v>30</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="3">
-        <v>35</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="3">
-        <v>40</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" t="s">
-        <v>46</v>
-      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>77</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,194 +1177,236 @@
         <v>96</v>
       </c>
       <c r="B39" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="B40" s="3">
+        <v>40</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="3">
+        <v>35</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="3">
+        <v>30</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" t="s">
-        <v>52</v>
+        <v>106</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="3">
-        <v>25</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="3">
-        <v>30</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" t="s">
-        <v>56</v>
-      </c>
+      <c r="E45" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
+        <v>30</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="3">
         <v>25</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" t="s">
-        <v>58</v>
+      <c r="C48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B49" s="3">
         <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B50" s="3">
         <v>25</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="3">
-        <v>25</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" t="s">
-        <v>65</v>
+      <c r="B52" s="3">
+        <v>30</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B53" s="3">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="3">
+        <v>25</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B54" s="3">
-        <v>30</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="3">
-        <v>20</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" t="s">
-        <v>72</v>
+      <c r="B56" s="3">
+        <v>60</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="3">
+        <v>30</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="3">
+        <v>20</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D60" t="s">
         <v>99</v>
       </c>
     </row>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B301214C-6240-4222-BE52-14EB200BD93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3104889-176C-4041-A884-114EA3901557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25830" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="115">
   <si>
     <t>Category</t>
   </si>
@@ -102,15 +102,6 @@
     <t>Reason + Act loop, step-by-step reasoning with tool usage</t>
   </si>
   <si>
-    <t>Few-shot vs Zero-shot</t>
-  </si>
-  <si>
-    <t>Examples for guiding agent behavior</t>
-  </si>
-  <si>
-    <t>ReAct Architecture</t>
-  </si>
-  <si>
     <t>Plan-and-Execute Agents</t>
   </si>
   <si>
@@ -159,9 +150,6 @@
     <t>Build Simple Agent (Python)</t>
   </si>
   <si>
-    <t>Agent with Memory</t>
-  </si>
-  <si>
     <t>RAG + Agent</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
     <t>Task Automation Agent</t>
   </si>
   <si>
-    <t>Advanced Topics</t>
-  </si>
-  <si>
     <t>Agent Evaluation</t>
   </si>
   <si>
@@ -189,9 +174,6 @@
     <t>Guardrails &amp; Safety</t>
   </si>
   <si>
-    <t>Limiting agent actions, validation, security concerns</t>
-  </si>
-  <si>
     <t>Cost Optimization</t>
   </si>
   <si>
@@ -246,9 +228,6 @@
     <t>Trends, AGI discussion, opportunities</t>
   </si>
   <si>
-    <t>pdf status</t>
-  </si>
-  <si>
     <t>pdf done</t>
   </si>
   <si>
@@ -360,9 +339,6 @@
     <t>done</t>
   </si>
   <si>
-    <t>Add memory using vector DB (Using FAISS)</t>
-  </si>
-  <si>
     <t>pdf + code done for ST/LT Memory</t>
   </si>
   <si>
@@ -370,6 +346,30 @@
   </si>
   <si>
     <t>Simple reflex agent, Model agent, goal based, utility based agent, Learning agent, LLM agent</t>
+  </si>
+  <si>
+    <t>For automation, see the automation directory</t>
+  </si>
+  <si>
+    <t>Limiting agent actions, Human in the loop,validation, security concerns</t>
+  </si>
+  <si>
+    <t>7 Advanced Topics</t>
+  </si>
+  <si>
+    <t>ReAct Architecture - Reactive Agents</t>
+  </si>
+  <si>
+    <t>pdf_code status</t>
+  </si>
+  <si>
+    <t>7 Advanced Topics (EXTRA)</t>
+  </si>
+  <si>
+    <t>MCP</t>
+  </si>
+  <si>
+    <t>Model Context Protocol</t>
   </si>
 </sst>
 </file>
@@ -711,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -735,12 +735,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -752,12 +752,12 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3">
         <v>25</v>
@@ -769,12 +769,12 @@
         <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -786,24 +786,24 @@
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -811,7 +811,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3">
         <v>30</v>
@@ -823,12 +823,12 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3">
         <v>25</v>
@@ -840,29 +840,29 @@
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B10" s="3">
         <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B11" s="3">
         <v>25</v>
@@ -874,12 +874,12 @@
         <v>16</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3">
         <v>30</v>
@@ -891,12 +891,12 @@
         <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3">
         <v>20</v>
@@ -908,506 +908,502 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="3">
-        <v>25</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="3">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="3">
-        <v>30</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3">
+        <v>30</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="3">
+        <v>30</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C23" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B24" s="3">
+        <v>25</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>78</v>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="4"/>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="3">
-        <v>30</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="3">
-        <v>30</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="3">
-        <v>25</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" t="s">
-        <v>38</v>
-      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B32" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B33" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>69</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>83</v>
+      </c>
+      <c r="B34" s="3">
+        <v>25</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="3">
+        <v>25</v>
+      </c>
       <c r="C35" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>108</v>
+        <v>36</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D36" s="4"/>
-      <c r="E36" s="3"/>
+      <c r="A36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="3">
+        <v>20</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="3">
-        <v>30</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" t="s">
-        <v>77</v>
+        <v>100</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="3">
-        <v>35</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="3">
-        <v>40</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" t="s">
-        <v>46</v>
-      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B41" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>70</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B42" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="B43" s="3">
+        <v>35</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="B44" s="3">
+        <v>30</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
+      </c>
+      <c r="D44" t="s">
+        <v>73</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="3"/>
+      <c r="A45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="3">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="3">
         <v>30</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="3">
+      <c r="C50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" s="3">
         <v>25</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="3">
-        <v>30</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3">
-        <v>25</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="B52" s="3">
         <v>30</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="B53" s="3">
         <v>25</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3">
+        <v>30</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="3">
+        <v>25</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="3">
+        <v>25</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="3">
+        <v>60</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" t="s">
         <v>62</v>
       </c>
-      <c r="D53" t="s">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3">
+        <v>30</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="3">
-        <v>25</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="D61" t="s">
         <v>64</v>
       </c>
-      <c r="D54" t="s">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+      <c r="D62" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="3">
-        <v>60</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="3">
-        <v>30</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="3">
-        <v>20</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" t="s">
-        <v>99</v>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
